--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0072.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0072.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hạt hơi đắng</t>
+          <t>Hạt có vị đắng nhẹ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bình lắc vệ sinh</t>
+          <t>Làm sạch bình lắc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Event Lối chơi</t>
+          <t>Nội dung sự kiện</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hủy Theo dõi</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MAX</t>
+          <t>TỐI ĐA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể thêm tối đa 2 Phụ gia</t>
+          <t>Cậu chỉ có thể thêm tối đa 2 Phụ Kiện thôi.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Cấp Độ Vibe</t>
+          <t>Cấp Độ Nhịp Điệu</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Unlocked Content</t>
+          <t>Nội dung đã mở khóa</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Vibe Gauge</t>
+          <t>Thang Đo Cảm Xúc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Phần thưởng theo cấp</t>
+          <t>Các phần thưởng Nhiệm vụ</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Pha đồ uống cho 3 người bạn đồng hành</t>
+          <t>Pha nước cho 3 người đồng hành</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thu thập 6 bức ảnh Fest Stars trong Sổ Kỷ Niệm</t>
+          <t>Thu thập 6 bức ảnh Ngôi sao Lễ hội trong Sách Kỷ niệm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Thu thập 8 bức ảnh Roamer's Ticks trong Sổ Kỷ Niệm</t>
+          <t>Thu thập 8 bức ảnh "Dấu Vết Lang Thang" trong Sổ Kỷ Niệm</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Thu thập tất cả ảnh trong bộ sưu tập Lollo Joy</t>
+          <t>Thu thập toàn bộ ảnh trong Bộ Sưu Tập Vui Vẻ của Lollo.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sử dụng Chỉnh sửa nhanh một lần trong Trang trí Tiệc tùng</t>
+          <t>Dùng Fast Decorate một lần trong Party Decor</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Trưng bày Giá trưng bày Echo một lần</t>
+          <t>Trưng bày Kệ Trưng Bày Echo một lần</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Trưng bày Giá trưng bày Vũ khí một lần</t>
+          <t>Trưng bày Kệ Trưng Bày Vũ Khí một lần</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đánh bại 3 người bạn đồng hành trong trò chơi bài</t>
+          <t>Đánh bại 3 đồng đội trong ván bài</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Pha đồ uống yêu thích cho 3 người bạn đồng hành</t>
+          <t>Pha 3 ly đồ uống yêu thích của đồng đội</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Trang trí đầy đủ 3 khu vực trong Trang trí Tiệc tùng</t>
+          <t>Trang trí đầy đủ 3 khu vực trong Trại Đội</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Trang trí đầy đủ 6 khu vực trong Trang trí Tiệc tùng</t>
+          <t>Trang trí đầy đủ 6 khu vực trong Trang Trí Bữa Tiệc</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trang trí đầy đủ 7 khu vực trong Trang trí Tiệc tùng</t>
+          <t>Trang trí đầy đủ 7 khu vực trong Trang Trí Bữa Tiệc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thu thập 20 vật trang trí</t>
+          <t>Thu thập 20 món đồ trang trí</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Thu thập 40 vật trang trí</t>
+          <t>Thu thập 40 món đồ trang trí</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Thu thập 100 vật trang trí</t>
+          <t>Thu thập 100 món đồ trang trí</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Nói chuyện với Cobb Copo để thay đổi thiết kế sàn</t>
+          <t>Trao đổi với Cobb Copo để thay đổi thiết kế tầng</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Chuyển cài đặt Bầu Trời Đêm (Mở khóa khi đạt Cấp Độ Vibe 8)</t>
+          <t>Đổi thiết lập Bầu Trời Đêm (Mở khóa khi đạt Cấp Độ Vibe 8)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trưng bày vật trang trí do bạn đồng hành tặng</t>
+          <t>Trưng bày món đồ trang trí do bạn đồng hành tặng</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đạt 6.000 điểm Vibe Gauge</t>
+          <t>Tích lũy 6.000 điểm Thanh Âm</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đạt 12.000 điểm Vibe Gauge</t>
+          <t>Tích lũy 12.000 điểm Thanh Âm</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tiếp tục Nhiệm Vụ Sự Kiện "Nơi Những Vì Sao Rơi Xuống" để mở khóa Pha Chế Đồ Uống</t>
+          <t>Tiếp tục Nhiệm Vụ Sự Kiện "Nơi Sao Rơi" để mở khóa chế tạo thức uống</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Có thể mời Cartethyia sau khi pha đồ uống mà Lupa thích</t>
+          <t>Có thể mời Cartethyia sau khi pha được thức uống mà Lupa thích</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Có thể mời Mornye sau khi pha đồ uống mà Cartethyia thích</t>
+          <t>Bạn có thể mời Mornye sau khi chuẩn bị một thức uống mà Cartethyia thích</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Make New Drink</t>
+          <t>Pha Thức Uống Mới</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Forever Fest và Lollo Party" và đạt Cấp Độ Vibe 3</t>
+          <t>Hoàn thành Nhiệm vụ "Lễ hội bất tận và Bữa tiệc Lollo" và đạt Cấp Độ Vibe 3</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Những Vì Sao Rơi" và đạt Cấp Độ Vibe 5</t>
+          <t>Hoàn thành Nhiệm vụ "Sao băng rơi" và đạt Cấp Độ Vibe 5</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Câu Trả Lời Nằm Nơi Dòng Sông Sao Rơi"</t>
+          <t>Hoàn thành Nhiệm vụ "Câu trả lời nằm nơi dòng sông sao rơi"</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Invite</t>
+          <t>Mời</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Invite Again</t>
+          <t>Mời lại</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đạt Giai Đoạn Platform</t>
+          <t>Đến Giai Đoạn Bệ Đáp</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Đạt Giai Đoạn Overwatch</t>
+          <t>Đến Giai Đoạn Giám Sát</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả các Giai Đoạn và xây dựng lại hoàn toàn Spacetrek Observatory</t>
+          <t>Hoàn thành tất cả các Giai Đoạn và tái thiết hoàn toàn Đài Thiên Văn Spacetrek.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Xây dựng lại Đường Cao Tốc Observatory-Academy</t>
+          <t>Tái thiết Xa Lộ Đài Thiên Văn - Học Viện</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Xây dựng lại Lối Đi Orbit Valley - Phía Bắc</t>
+          <t>Tái thiết Đèo Thung Lũng Quỹ Đạo - Phía Bắc</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Xây dựng lại Lối Đi Orbit Valley - Phía Nam</t>
+          <t>Khôi phục Đèo Orbit Valley - Nam</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Xây dựng lại Sandreach Passage</t>
+          <t>Khôi phục Hành lang Sandreach</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Xây dựng lại Con Đường Người Lữ Hành</t>
+          <t>Tái thiết Con Đường Người Lang Thang</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Xây dựng lại Spacetrek–Bjartr Bridge</t>
+          <t>Khôi phục Cầu Spacetrek–Bjartr</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Xây dựng lại Starleap Ascent</t>
+          <t>Khôi phục Starleap Ascent</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Xây dựng lại Howling Tunnel</t>
+          <t>Tái thiết Đường Hầm Gió Hú</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Xây dựng lại Vòng Tay Của Sol</t>
+          <t>Khôi phục Sol's Embrace</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Xây dựng lại Submerged Tunnel</t>
+          <t>Khôi phục Đường hầm Ngập nước</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Điều chỉnh Thời gian bị khóa hoặc không khả dụng</t>
+          <t>Điều Chỉnh Thời Gian bị khóa hoặc không khả dụng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Lobby</t>
+          <t>Sảnh chính</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Quầy bar</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Thư Viện Sưu Tập</t>
+          <t>Bộ sưu tập</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Outdoor Lounge</t>
+          <t>Khu Nghỉ Dưỡng Ngoài Trời</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Vườn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Screening Room</t>
+          <t>Phòng Chiếu</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Học tập</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Đồng Hồ Sức Sống Khu Vực</t>
+          <t>Đồng hồ Tần số Khu vực</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Khu vực</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cửa hàng trang trí</t>
+          <t>Cửa Hàng Trang Trí</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Danh Mục Trang Trí</t>
+          <t>Bộ Sưu Tập Trang Trí</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Trang Trí Khu Vực</t>
+          <t>Trang trí khu vực</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Decoration Complete</t>
+          <t>Hoàn Thành Trang Trí</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đã lưu thiết kế hiện tại</t>
+          <t>Thiết kế hiện tại đã được lưu.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Chuyển sang camera Tổng quan</t>
+          <t>Đã chuyển sang camera Tổng Quan</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Exited Overview Camera</t>
+          <t>Đã thoát Chế Độ Quan Sát Toàn Cảnh</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Thoát và Lưu thiết kế</t>
+          <t>Thoát và Lưu Thiết Kế</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Lưu và Thoát</t>
+          <t>Lưu và thoát</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Switch Area</t>
+          <t>Chuyển khu vực</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Lưu và Chuyển đổi</t>
+          <t>Lưu và chuyển đổi</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Decor Details</t>
+          <t>Chi Tiết Trang Trí</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đến Cửa hàng Trang trí</t>
+          <t>Đến Cửa Hàng Trang Trí</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Quà Tặng Của Resonator</t>
+          <t>Quà tặng Resonator</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Món quà của Resonator không khả dụng</t>
+          <t>Không có Quà tặng Resonator</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Trang Trí Nhanh</t>
+          <t>Trang trí Nhanh</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Trang Trí Nhanh</t>
+          <t>Trang trí Nhanh</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vùng Đất Thưởng Thức</t>
+          <t>Vùng Đất Thụ Hưởng</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Kho Tàng Vinh Quang</t>
+          <t>Kho Báu Vinh Quang</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Vườn Hoa Đêm</t>
+          <t>Vườn Hoa Nở Đêm</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Sân Vườn Phiêu Lưu</t>
+          <t>Sân Phiêu Lưu</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Themed Decorations ({0}/{1})</t>
+          <t>Trang Trí Chủ Đề ({0}/{1})</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Đến Cửa hàng Trang trí</t>
+          <t>Đến Cửa Hàng Trang Trí</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Trang Trí Nhanh</t>
+          <t>Trang trí Nhanh</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Áp Dụng Thiết Kế Hiện Tại</t>
+          <t>Áp dụng Thiết Kế Hiện Tại</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Mua &amp; Trang trí</t>
+          <t>Mua &amp; Trang Trí</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Trang Trí Nhanh</t>
+          <t>Trang trí Nhanh</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Fast Decoration Complete</t>
+          <t>Hoàn tất Trang trí Nhanh</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Danh Mục Trang Trí</t>
+          <t>Bộ Sưu Tập Trang Trí</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Vibe Gauge</t>
+          <t>Thang Đo Cảm Xúc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Cửa hàng trang trí</t>
+          <t>Cửa Hàng Trang Trí</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Decor Details</t>
+          <t>Chi Tiết Trang Trí</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Insufficient Starfall Coins</t>
+          <t>Không đủ Xu Sao Rơi</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Azure Lawn</t>
+          <t>Bãi Cỏ Lam</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Azure Lawn</t>
+          <t>Bãi Cỏ Lam</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Azure Lawn</t>
+          <t>Bãi Cỏ Lam</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Autumn Lawn</t>
+          <t>Bãi Cỏ Mùa Thu</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Autumn Lawn</t>
+          <t>Bãi Cỏ Mùa Thu</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Autumn Lawn</t>
+          <t>Bãi Cỏ Mùa Thu</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Natural Lawn</t>
+          <t>Bãi Cỏ Tự Nhiên</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Natural Lawn</t>
+          <t>Bãi Cỏ Tự Nhiên</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Natural Lawn</t>
+          <t>Bãi Cỏ Tự Nhiên</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Simple Screen</t>
+          <t>Màn Hình Đơn Giản</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Ragunna Screen</t>
+          <t>Màn hình Ragunna</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Paradox Orrery</t>
+          <t>Cỗ Máy Nghịch Lý</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Chirpuff Pillow</t>
+          <t>Gối Chirpuff</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Gulpuff Pillow</t>
+          <t>Gối Gulpuff</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Diggy Duggy Pillow</t>
+          <t>Gối Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Carnevale Balloon</t>
+          <t>Bong Bóng Carnevale</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Laureate Balloon</t>
+          <t>Bong bóng Vinh Danh</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Dreamscape Swim Ring</t>
+          <t>Vòng Bơi Mộng Ảo</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Averardo Floor Clock</t>
+          <t>Đồng Hồ Tầng Averardo</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Vessel Floor Clock</t>
+          <t>Đồng Hồ Tầng Vỏ</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Calendula Floor Clock</t>
+          <t>Đồng hồ Calendula</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Water Purifier</t>
+          <t>Máy Lọc Nước</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Averardo Floor Lamp</t>
+          <t>Đèn Sàn Averardo</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Tentacle Floor Lamp</t>
+          <t>Đèn Sàn Xúc Tu</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Classical Lute</t>
+          <t>Đàn Luýt Cổ Điển</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Improv Lute</t>
+          <t>Đàn Lute Ứng Tác</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Ragunna Small Lamp</t>
+          <t>Đèn Ngủ Nhỏ Ragunna</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Sonata Organ Cart</t>
+          <t>Xe Organ Sonata</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tidecaller Horn</t>
+          <t>Tù Và Gọi Triều</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Tales of the Isles: Bộ Sưu Tập Mới Nhất</t>
+          <t>Huyền Thoại Quần Đảo: Tuyển Tập Mới Nhất</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Elegant Table Lamp</t>
+          <t>Đèn Bàn Thanh Lịch</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Pumpkin</t>
+          <t>Bí Ngô</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Melon</t>
+          <t>Dưa</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Cheese Wheel</t>
+          <t>Bánh Phô Mai</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Imperator's Balance</t>
+          <t>Sự Cân Bằng của Đại Đế</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Chocolate Waterfall</t>
+          <t>Thác Sô-cô-la</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ammonoid Table Clock</t>
+          <t>Đồng Hồ Ammonoid</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Free-Standing Display Cabinet</t>
+          <t>Tủ Trưng Bày Tự Đứng</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Display Cabinet</t>
+          <t>Tủ trưng bày tiêu chuẩn</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Elegant Fireplace</t>
+          <t>Lò Sưởi Thanh Lịch</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Azure Flowering Tree</t>
+          <t>Cây Hoa Lam Nở Rộ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Azure Flowering Tree</t>
+          <t>Cây Hoa Lam Nở Rộ</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Azure Flowering Tree</t>
+          <t>Cây Hoa Lam Nở Rộ</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Natural Flowering Tree</t>
+          <t>Cây Tự Nhiên Nở Hoa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Natural Flowering Tree</t>
+          <t>Cây Tự Nhiên Nở Hoa</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Natural Flowering Tree</t>
+          <t>Cây Tự Nhiên Nở Hoa</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Autumn Lantern</t>
+          <t>Đèn Lồng Mùa Thu</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Autumn Lantern</t>
+          <t>Đèn Lồng Mùa Thu</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Autumn Lantern</t>
+          <t>Đèn Lồng Mùa Thu</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Azure Hedge</t>
+          <t>Hàng Rào Lam</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Azure Hedge</t>
+          <t>Hàng Rào Lam</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Azure Hedge</t>
+          <t>Hàng Rào Lam</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Autumn Hedge</t>
+          <t>Hàng Rào Mùa Thu</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Autumn Hedge</t>
+          <t>Hàng Rào Mùa Thu</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Autumn Hedge</t>
+          <t>Hàng Rào Mùa Thu</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Bộ Bàn Ghế - Mặt Trời Rực Rỡ</t>
+          <t>Bộ Bàn Ghế - Nắng Gắt</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bộ Bàn Ghế - Tiệc Tùng</t>
+          <t>Bộ Bàn Ghế - Tiệc Lớn</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Bộ Bàn Ghế - Ánh Nắng Ấm Áp</t>
+          <t>Bộ Bàn Ghế - Ánh Dương Ấm</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Bộ Bàn Ghế - Đô Thị</t>
+          <t>Bộ Bàn Ghế - Thành Thị</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Bộ Bàn Ghế - Buổi Chiều</t>
+          <t>Bộ Bàn Ghế - Buổi Trưa</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Red Floral Arrangement</t>
+          <t>Bình Hoa Đỏ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Blue Floral Arrangement</t>
+          <t>Bình Hoa Xanh</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Di Chuyển Đến Đây</t>
+          <t>Dời đến đây</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Large Decorations</t>
+          <t>Trang trí cỡ lớn</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tabletop Decorations</t>
+          <t>Đồ Trang Trí Bàn Ăn</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Medium Decorations</t>
+          <t>Trang trí Cỡ Trung</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Plants - Flowers</t>
+          <t>Thực Vật - Hoa</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Plants - Grass</t>
+          <t>Thực Vật - Cỏ</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Plants - Trees</t>
+          <t>Thực Vật - Cây</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hãy tiến triển với Nhiệm Vụ Chính</t>
+          <t>Hãy tiếp tục hoàn thành Nhiệm Vụ Chính.</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Immediately Obtainable</t>
+          <t>Có thể nhận ngay</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Nhận cả hai bộ Avatar và Trang Phục cùng lúc</t>
+          <t>Nhận cả hai bộ Avatar và Trang phục cùng lúc.</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>TERM-X: Outreach</t>
+          <t>TERM-X: Truyền Tin</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Nhận để nhận thêm:</t>
+          <t>Nhận thêm:</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Cửa hàng trang trí</t>
+          <t>Cửa Hàng Trang Trí</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Danh Mục Trang Trí</t>
+          <t>Bộ Sưu Tập Trang Trí</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Septimont Floral Arrangement</t>
+          <t>Nghệ Thuật Cắm Hoa Septimont</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Pastoral Floral Arrangement</t>
+          <t>Bó Hoa Đồng Quê</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Study Floral Arrangement</t>
+          <t>Học Cắm Hoa</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Greenhouse Floral Arrangement</t>
+          <t>Bó Hoa Nhà Kính</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tidal Floral Arrangement</t>
+          <t>Nghệ thuật Cắm hoa Thủy Triều</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>"Griffrex's Fest" Canned Meat</t>
+          <t>"Thịt hộp 'Lễ Hội Griffrex'"</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Decor Set - Septimont</t>
+          <t>Bộ Trang Trí - Septimont</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Decor Set - Tides</t>
+          <t>Bộ Trang Trí - Thủy Triều</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Decor Set - Market</t>
+          <t>Bộ Trang Trí - Chợ</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Assorted Fruit Platter</t>
+          <t>Đĩa Trái cây Hỗn hợp</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Vibrant Fruit Platter</t>
+          <t>Mâm Trái Cây Tươi Mát</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Mixed Fruit Platter</t>
+          <t>Đĩa Trái Cây Hỗn Hợp</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ornament Set - Leisure</t>
+          <t>Bộ Trang Trí - Thư Giãn</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Bộ Đồ Trang Trí - Hoa &amp; Thơ</t>
+          <t>Bộ Trang Trí - Hoa &amp; Thơ</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Ornament Set - Cozy Afternoon Tea</t>
+          <t>Bộ Trang Trí - Chiều Thong Dong Uống Trà</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Edible Armament</t>
+          <t>Vũ Khí Ăn Được</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Hearty Afternoon Tea</t>
+          <t>Trà Chiều Ấm Áp</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Modern Afternoon Tea</t>
+          <t>Trà Chiều Hiện Đại</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Ragunna Vintage</t>
+          <t>Đồ Cổ Ragunna</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Septimont Vintage</t>
+          <t>Hương Vị Septimont Xưa</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Bar Vintage</t>
+          <t>Quán Bar Cổ Điển</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Elixir Vintage</t>
+          <t>Rượu Elixir Vintage</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Vintage of Time</t>
+          <t>Dấu Ấn Thời Gian</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Carnevale Gift</t>
+          <t>Món Quà Carnevale</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Childhood Dream Gift</t>
+          <t>Món Quà Mơ Ước Tuổi Thơ</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Margherita's Combo</t>
+          <t>Tổ Hợp Kỹ Năng Margherita</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Gladiator's Feast</t>
+          <t>Tiệc Chiến Binh</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Dessert Paradise</t>
+          <t>Thiên Đường Bánh Ngọt</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Solis Combo</t>
+          <t>Tổ Hợp Món Solis</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Mineral Display Rack</t>
+          <t>Kệ trưng bày khoáng vật</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Mineral Ornament</t>
+          <t>Đồ trang trí khoáng vật</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Averardo Writing Desk</t>
+          <t>Bàn Viết Averardo</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Montelli Wine Cabinet</t>
+          <t>Tủ Rượu Montelli</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Oak Wine Barrels</t>
+          <t>Thùng Rượu Sồi</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Bar Cabinet</t>
+          <t>Tủ rượu</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Wine Display Cabinet</t>
+          <t>Tủ Trưng Bày Rượu</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Soft Pink Lawn</t>
+          <t>Bãi Cỏ Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Pale Blue Lawn</t>
+          <t>Bãi Cỏ Xanh Nhạt</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Early Autumn Lawn</t>
+          <t>Bãi Cỏ Đầu Thu</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Soft Pink Lawn</t>
+          <t>Bãi Cỏ Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Pale Blue Lawn</t>
+          <t>Bãi Cỏ Xanh Nhạt</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Early Autumn Lawn</t>
+          <t>Bãi Cỏ Đầu Thu</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Soft Pink Lawn</t>
+          <t>Bãi Cỏ Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Pale Blue Lawn</t>
+          <t>Bãi Cỏ Xanh Nhạt</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Early Autumn Lawn</t>
+          <t>Bãi Cỏ Đầu Thu</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Soft Pink Flowerbed</t>
+          <t>Thảm Hoa Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Pale Blue Flowerbed</t>
+          <t>Luống Hoa Xanh Nhạt</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Early Autumn Flowerbed</t>
+          <t>Luống Hoa Đầu Thu</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Soft Pink Flowerbed</t>
+          <t>Thảm Hoa Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Pale Blue Flowerbed</t>
+          <t>Luống Hoa Xanh Nhạt</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Early Autumn Flowerbed</t>
+          <t>Luống Hoa Đầu Thu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Soft Pink Flowerbed</t>
+          <t>Thảm Hoa Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Pale Blue Flowerbed</t>
+          <t>Luống Hoa Xanh Nhạt</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Early Autumn Flowerbed</t>
+          <t>Luống Hoa Đầu Thu</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Soft Pink Tree</t>
+          <t>Cây Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Pale Blue Tree</t>
+          <t>Cây Xanh Nhạt</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Early Autumn Tree</t>
+          <t>Cây Đầu Thu</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Soft Pink Tree</t>
+          <t>Cây Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Pale Blue Tree</t>
+          <t>Cây Xanh Nhạt</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Early Autumn Tree</t>
+          <t>Cây Đầu Thu</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Soft Pink Tree</t>
+          <t>Cây Hồng Nhạt Mềm Mại</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Pale Blue Tree</t>
+          <t>Cây Xanh Nhạt</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Early Autumn Tree</t>
+          <t>Cây Đầu Thu</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>"Devil's Kiss"</t>
+          <t>Nụ hôn của Ác quỷ</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Jellyfish Night Light</t>
+          <t>Đèn Ngủ Sứa</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Worn Gulpuff Plushie</t>
+          <t>Thú Nhồi Bông Gulpuff Cũ</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Paint Set</t>
+          <t>Bộ Màu Vẽ</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Riot Blades Lv. 0</t>
+          <t>Lưỡi Kiếm Bạo Loạn Cấp 0</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Riot Blades Lv. 1</t>
+          <t>Lưỡi Kiếm Bạo Loạn Cấp 1</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Riot Blades Lv. 2</t>
+          <t>Lưỡi Kiếm Bạo Loạn Cấp 2</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Riot Blades Lv. 3</t>
+          <t>Lưỡi Kiếm Bạo Loạn Cấp 3</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Mind Shock Lv. 0</t>
+          <t>Sốc Tâm Thức Cấp 0</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Mind Shock Lv. 1</t>
+          <t>Sốc Tâm Thức Cấp 1</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Mind Shock Lv. 2</t>
+          <t>Sốc Tâm Thức Cấp 2</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mind Shock Lv. 3</t>
+          <t>Sốc Tâm Thức Cấp 3</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Impulse Tide Lv. 0</t>
+          <t>Sóng Xung Kích Cấp 0</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Impulse Tide Lv. 1</t>
+          <t>Sóng Xung Kích Cấp 1</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Impulse Tide Lv. 2</t>
+          <t>Sóng Xung Kích Cấp 2</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Impulse Tide Lv. 3</t>
+          <t>Sóng Xung Kích Cấp 3</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hypnotic Chant Lv. 0</t>
+          <t>Thánh Ca Thôi Miên Cấp 0</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Hypnotic Chant Lv. 1</t>
+          <t>Thánh Ca Thôi Miên Cấp 1</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hypnotic Chant Lv. 2</t>
+          <t>Thánh Ca Thôi Miên Cấp 2</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hypnotic Chant Lv. 3</t>
+          <t>Thánh Ca Thôi Miên Cấp 3</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Piercing Claw Lv. 0</t>
+          <t>Vuốt Xuyên Thấu Cấp 0</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Piercing Claw Lv. 1</t>
+          <t>Móng Vuốt Xuyên Thấu Cấp 1</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Piercing Claw Lv. 2</t>
+          <t>Móng Vuốt Xuyên Thấu Cấp 2</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Piercing Claw Lv. 3</t>
+          <t>Móng Vuốt Xuyên Thấu Cấp 3</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Budget Dilemma Lv. 0</t>
+          <t>Tiến Thoái Lưỡng Nan Cấp 0</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Budget Dilemma Lv. 1</t>
+          <t>Tiến Thoái Lưỡng Nan Cấp 1</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Budget Dilemma Lv. 2</t>
+          <t>Tiến Thoái Lưỡng Nan Cấp 2</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Budget Dilemma Lv. 3</t>
+          <t>Tiến Thoái Lưỡng Nan Cấp 3</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "Lahai-Roi: Become Beast"</t>
+          <t>Thu thập 80.000 Xu trong "Lahai-Roi: Hóa Thú"</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "Mechanical Dawn"</t>
+          <t>Thu thập 80.000 Xu trong "Bình Minh Cơ Khí"</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "I, Biomech"</t>
+          <t>Thu thập 80.000 Xu trong "Ta Là Sinh Cơ"</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "Diva Dance"</t>
+          <t>Thu thập 80.000 Xu trong "Vũ Điệu Diva"</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "True Steel"</t>
+          <t>Thu thập 80.000 Xu trong "Thép Chân Chính"</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Thu thập 80.000 Coin trong "Funds Never Sleep"</t>
+          <t>Thu thập 80.000 Xu trong "Tiền Không Ngủ"</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Đã mở khóa Phonograph</t>
+          <t>Máy quay đĩa đã mở khóa</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Echo Display</t>
+          <t>Bản Trình Chiếu Tiếng Vọng</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>The "Bar" Area</t>
+          <t>Khu vực "Quán Bar"</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Một vật trang trí cố định mới tại Khu vực Lễ hội</t>
+          <t>Một vật trang trí cố định mới tại Khu Hội Chợ</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>The "Thư Viện Sưu Tập" Area</t>
+          <t>Khu vực "Bảo Tàng Sưu Tập"</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>The "Outdoor Lounge" Area</t>
+          <t>Khu vực "Sân Thưởng Ngoại"</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>The "Screening Room" Area</t>
+          <t>Khu vực "Phòng Chiếu Phim"</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>The "Garden" Area</t>
+          <t>Khu vực "Vườn"</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tính năng Trang trí Nhanh</t>
+          <t>Tính năng Trang Trí Nhanh</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Một vật trang trí cố định mới tại Khu vực Lễ hội</t>
+          <t>Một vật trang trí cố định mới tại Khu Hội Chợ</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>The "Study" Area</t>
+          <t>Khu Vực "Nghiên Cứu"</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Tính năng Chuyển đổi Bầu trời Đêm</t>
+          <t>Tính năng Chuyển Đổi Bầu Trời Đêm</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ sự kiện và chuẩn bị cho Lễ hội</t>
+          <t>Hoàn thành nhiệm vụ sự kiện và chuẩn bị cho Lễ Hội</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Chơi trò chơi tại Lễ hội</t>
+          <t>Tham gia các trò chơi tại Lễ Hội</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Trang trí Khu vực Lễ hội</t>
+          <t>Trang Hoàng Khu Vực Lễ Hội</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Event Lối chơi</t>
+          <t>Nội dung sự kiện</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Achievement Tasks</t>
+          <t>Nhiệm vụ Thành tựu</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Mở khóa xe máy thám hiểm trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "What Burns Beneath Frostlands"</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Bạn hiện không ở trong môi trường sự kiện</t>
+          <t>Hiện tại cậu không ở trong môi trường sự kiện</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Lobby I</t>
+          <t>Sảnh I</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Lobby II</t>
+          <t>Sảnh II</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Lobby III</t>
+          <t>Sảnh III</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Bar I</t>
+          <t>Quầy bar này...</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Bar II</t>
+          <t>Quán Bar II</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Bar III</t>
+          <t>Quán Bar III</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Screening Room I</t>
+          <t>Phòng Chiếu I</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Screening Room II</t>
+          <t>Phòng Chiếu II</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Screening Room III</t>
+          <t>Phòng Chiếu III</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Outdoor Lounge I</t>
+          <t>Khu Nghỉ Dưỡng Ngoài Trời I</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Outdoor Lounge II</t>
+          <t>Khu Nghỉ Dưỡng Ngoài Trời II</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Outdoor Lounge III</t>
+          <t>Khu Giải Trí Ngoài Trời III</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Thư Viện Sưu Tập I</t>
+          <t>Bộ sưu tập I</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Thư Viện Sưu Tập II</t>
+          <t>Bộ Sưu Tập II</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Thư Viện Sưu Tập III</t>
+          <t>Bộ Sưu Tập III</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Garden I</t>
+          <t>Vườn I</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Garden II</t>
+          <t>Vườn II</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Garden III</t>
+          <t>Vườn III</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Study I</t>
+          <t>Bài Học I</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Study II</t>
+          <t>Bài Học II</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Study III</t>
+          <t>Bài Học III</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Cuddle Wuddle Bean Bag Chair</t>
+          <t>Ghế Ôm Cuddle Wuddle</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Cấu hình sự kiện không tồn tại</t>
+          <t>Cấu hình sự kiện không tồn tại.</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Thành phần sự kiện không tồn tại</t>
+          <t>Thành phần sự kiện không tồn tại.</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Dữ liệu vận hành sự kiện không tồn tại</t>
+          <t>Không tìm thấy dữ liệu hoạt động của sự kiện</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Không thể yêu cầu trong Chế độ Hợp Tác</t>
+          <t>Không thể gửi yêu cầu trong Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Cấu hình mở khóa chức năng sự kiện không tồn tại</t>
+          <t>Không tìm thấy cấu hình mở khóa chức năng sự kiện</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>ID sự kiện không khớp</t>
+          <t>ID Sự kiện không trùng khớp</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Khu vực không thuộc sự kiện này</t>
+          <t>Khu vực này không thuộc sự kiện này</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cấu hình ô không tồn tại</t>
+          <t>Cấu hình khe không tồn tại</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Khu vực người chơi bị khóa, không có dữ liệu</t>
+          <t>Khu vực của người chơi bị khóa, không có dữ liệu</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Số lượng Decoration không hợp lệ</t>
+          <t>Số lượng Trang trí không hợp lệ</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể không phải loại ô</t>
+          <t>Cấu hình thực thể không phải loại khe</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Nhiều thực thể tồn tại trong ô bản đồ</t>
+          <t>Có nhiều thực thể tồn tại trong ô bản đồ</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Số lượng trang trí phụ và ô không khớp</t>
+          <t>Số lượng phụ kiện trang trí và ô trống không khớp.</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tạo thực thể thất bại</t>
+          <t>Không tạo được thực thể</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Độ dài danh sách trang trí phụ không được bằng 0 khi xóa trang trí</t>
+          <t>Danh sách phụ kiện trang trí không được để trống khi xóa trang trí</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Danh sách nhóm thực thể trống</t>
+          <t>Danh sách nhóm thực thể trống rỗng</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Chuyển đổi short ID thất bại</t>
+          <t>Không chuyển đổi được ID ngắn</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Khe trang trí đã tồn tại</t>
+          <t>Ô trang trí đã tồn tại</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Đồ nội thất đã mở khóa</t>
+          <t>Đã mở khóa nội thất</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Không tìm thấy mục trong tập tài liệu</t>
+          <t>Không tìm thấy mục giới thiệu</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Mục trong tập tài liệu đã tồn tại</t>
+          <t>Mục tập tài liệu đã tồn tại</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Cấu hình mục trong tập tài liệu không tồn tại</t>
+          <t>Cấu hình mục tập tài liệu không tồn tại</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Mục trong tập tài liệu chưa hoàn thành</t>
+          <t>Mục nhập trong tập tài liệu chưa hoàn thành</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng mục trong tập tài liệu</t>
+          <t>Đã nhận phần thưởng mục nhập trong tập tài liệu</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tập tài liệu chưa khả dụng</t>
+          <t>Tập tài liệu chưa mở khóa</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Mục không thuộc tập tài liệu này</t>
+          <t>Mục này không thuộc tập tài liệu này</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Bản nhạc máy hát không tồn tại</t>
+          <t>Không có bản nhạc nào trong máy hát</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Mục này bị khóa</t>
+          <t>Mục này đã bị khóa</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Exam 1</t>
+          <t>Bài kiểm tra 1</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Exam 2</t>
+          <t>Bài kiểm tra 2</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Exam 3</t>
+          <t>Bài kiểm tra 3</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Exam 4</t>
+          <t>Bài kiểm tra 4</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Exam 5</t>
+          <t>Bài kiểm tra 5</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Exam 6</t>
+          <t>Bài kiểm tra 6</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Exam 7</t>
+          <t>Bài kiểm tra 7</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Exam 8</t>
+          <t>Bài kiểm tra 8</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Pass Exam 1</t>
+          <t>Vượt qua Bài Kiểm Tra 1</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Pass Exam 2</t>
+          <t>Vượt qua Bài Kiểm Tra 2</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Pass Exam 3</t>
+          <t>Vượt qua Bài Kiểm Tra 3</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Pass Exam 4</t>
+          <t>Vượt qua Bài Kiểm Tra 4</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Pass Exam 5</t>
+          <t>Vượt qua Bài Kiểm Tra 5</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Pass Exam 6</t>
+          <t>Vượt qua Bài Kiểm Tra 6</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Pass Exam 7</t>
+          <t>Vượt qua Bài Kiểm Tra 7</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Vượt qua tất cả các bài kiểm tra</t>
+          <t>Vượt qua tất cả các kỳ thi</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ GPA 500</t>
+          <t>Đạt Cấp GPA 500</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ GPA 700</t>
+          <t>Đạt Cấp GPA 700</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Không Bonus</t>
+          <t>Không có thưởng</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Strike</t>
+          <t>Tấn công!</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Strike</t>
+          <t>Tấn công!</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Critical Hit</t>
+          <t>Bạo Kích</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Nghệ Thuật Phản Công</t>
+          <t>Nghệ thuật Phản Công</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Critical Hit</t>
+          <t>Bạo Kích</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Off-Field Aid</t>
+          <t>Hỗ Trợ Ngoài Chiến Trường</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Critical Hit: Ardent</t>
+          <t>Bạo Kích: Nồng Nhiệt</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Critical Hit: Ardent</t>
+          <t>Bạo Kích: Nồng Nhiệt</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nature's Gift</t>
+          <t>Món Quà Của Tự Nhiên</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Không Bonus</t>
+          <t>Không có thưởng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Không Bonus</t>
+          <t>Không có thưởng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ Kho Báu Hoang Dã</t>
+          <t>Kho Báu Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Nhanh lên! Dự Án Công Cụ Hóa F.U.E.L.!</t>
+          <t>Tăng tốc nào! Dự án Công Cụ Hóa Nhiên Liệu F.U.E.L.!</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Tốc Độ</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Plate Size</t>
+          <t>Kích Thước Đĩa</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Energy Regen</t>
+          <t>Hồi Năng Lượng</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Secret Diner</t>
+          <t>Quán Ăn Bí Mật</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Secret Diners To Be Introduced</t>
+          <t>Những Quán Ăn Bí Mật Sẽ Được Giới Thiệu</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Ngã Tư Trên Đường: Dễ</t>
+          <t>Thánh Giá Trên Đường Đua: Dễ</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Ngã Tư Trên Đường: Khó</t>
+          <t>Thánh Giá Trên Đường Đua: Khó</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>The Opposing Colors: Easy</t>
+          <t>Màu Đối Lập: Dễ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>The Opposing Colors: Khó</t>
+          <t>Màu Đối Lập: Khó</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>The Starward Greatsword: Easy</t>
+          <t>Kiếm Đại Ngôi Sao: Dễ</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>The Starward Greatsword: Khó</t>
+          <t>Kiếm Đại Ngôi Sao: Khó</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>The Trapped Stars: Easy</t>
+          <t>Những Vì Sao Bị Giam Cầm: Dễ</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>The Trapped Stars: Khó</t>
+          <t>Những Vì Sao Bị Giam Cầm: Khó</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>The Yearning Heart: Easy</t>
+          <t>Trái Tim Khao Khát: Dễ</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>The Yearning Heart: Khó</t>
+          <t>Trái Tim Khao Khát: Khó</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>The Masked Face: Easy</t>
+          <t>Khuôn Mặt Đeo Mặt Nạ: Dễ</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>The Masked Face: Khó</t>
+          <t>Khuôn Mặt Che Mặt: Cứng Rắn</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>The Sealed Gate: Easy</t>
+          <t>Cánh Cổng Bị Phong Ấn: Dễ</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>The Sealed Gate: Khó</t>
+          <t>Cánh Cổng Bị Phong Ấn: Khó</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Ngã Tư Trên Đường</t>
+          <t>Thánh Giá Trên Đường Đua</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>The Opposing Colors</t>
+          <t>Màu Đối Lập</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>The Starward Greatsword</t>
+          <t>Kiếm Đại Ngôi Sao</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>The Trapped Stars</t>
+          <t>Những Vì Sao Bị Giam Cầm</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>The Yearning Heart</t>
+          <t>Trái Tim Khao Khát</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>The Masked Face</t>
+          <t>Khuôn Mặt Đeo Mặt Nạ</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>The Sealed Gate</t>
+          <t>Cánh Cổng Bị Phong Ấn</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu gameplay trong khi đang tương tác</t>
+          <t>Không thể bắt đầu trò chơi khi đang tương tác</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Dành Cho Người Đi Trong Tuyết</t>
+          <t>Vì người bước đi trong tuyết</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Bay Lượn Trong Mùa Xuân</t>
+          <t>Bay Lượn Mùa Xuân</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>When Winter Thaws</t>
+          <t>Khi Mùa Đông Tan</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Everbright Polestar</t>
+          <t>Ngôi Sao Bắc Đẩu Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Everbright Polestar</t>
+          <t>Ngôi Sao Bắc Đẩu Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Chương III Hồi III "Ngôi Sao Hành Hương Xa Xôi"</t>
+          <t>Chương III Hồi III "Ngôi Sao Lang Thang Xa Xôi"</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Chuyển Tiếp: Ngoại Truyện "Tất Cả Những Ánh Nắng Chạm Đến"</t>
+          <t>Chuyển cảnh: Ngoại truyện "Tất Cả Những Gì Ánh Mặt Trời Chạm Đến"</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Ngôi Sao Hành Hương Xa</t>
+          <t>Ngôi Sao Viễn Du</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Roya Frostlands: Frostlands Surface</t>
+          <t>Vùng Đất Băng Giá Roya: Bề Mặt Lãnh Nguyên</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Tidelost Forest</t>
+          <t>Rừng Thủy Triều Lạc Lối</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
